--- a/public/exports-with-coowners/29188475.xlsx
+++ b/public/exports-with-coowners/29188475.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526270</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526267</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562929</t>
+          <t xml:space="preserve">311562931</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562920</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562915</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562916</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562926</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562919</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M130" t="inlineStr">

--- a/public/exports-with-coowners/29188475.xlsx
+++ b/public/exports-with-coowners/29188475.xlsx
@@ -4039,7 +4039,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526266</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526267</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562931</t>
+          <t xml:space="preserve">311562932</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562912</t>
+          <t xml:space="preserve">311562928</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562920</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562913</t>
+          <t xml:space="preserve">311562928</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562914</t>
+          <t xml:space="preserve">311562928</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562915</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562916</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562919</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562921</t>
+          <t xml:space="preserve">311562924</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">

--- a/public/exports-with-coowners/29188475.xlsx
+++ b/public/exports-with-coowners/29188475.xlsx
@@ -4039,7 +4039,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526269</t>
+          <t xml:space="preserve">311526266</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311526270</t>
+          <t xml:space="preserve">311526269</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562932</t>
+          <t xml:space="preserve">311562929</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562928</t>
+          <t xml:space="preserve">311562912</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562928</t>
+          <t xml:space="preserve">311562913</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562928</t>
+          <t xml:space="preserve">311562914</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562926</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562924</t>
+          <t xml:space="preserve">311562921</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M131" t="inlineStr">
